--- a/i18n/strings.xlsx
+++ b/i18n/strings.xlsx
@@ -655,7 +655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -830,6 +830,40 @@
       <c r="C10" t="inlineStr">
         <is>
           <t>保存</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>result_save_to_detail</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Save &amp; Update Detail</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>保存更新详情页</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>result_save_to_home</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Save &amp; Update Home</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>保存更新首页</t>
         </is>
       </c>
     </row>

--- a/i18n/strings.xlsx
+++ b/i18n/strings.xlsx
@@ -446,12 +446,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>My App</t>
+          <t>Short Video</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>我的应用</t>
+          <t>短视频</t>
         </is>
       </c>
     </row>
